--- a/public/data/6-9-25/khos.xlsx
+++ b/public/data/6-9-25/khos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARVIN3108\Desktop\au-tryout-statistics\public\data\6-9-25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1397459D-9A68-4F8A-8D8D-F0F296A7133D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77317981-A9A5-4E06-9BE4-8BB81460C8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -400,7 +400,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -452,7 +452,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
